--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0114.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0114.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Hello.</t>
+          <t>Xin chào.</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Ở quê nhà... việc trở thành Cộng Hưởng Giả không được chấp nhận.</t>
+          <t>Ở quê nhà... việc trở thành Resonator không được chấp nhận.</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Ánh sáng tốt và tầm nhìn tốt, đó là tất cả những gì ta cần.</t>
+          <t>Ánh sáng tốt và tầm nhìn tốt, đó là tất cả những gì tao cần.</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Ta... đã gặp ngươi ở đâu rồi nhỉ? Có phải trong bài báo đang lan truyền kia không?</t>
+          <t>Tao... đã gặp mày ở đâu rồi nhỉ? Có phải trong bài báo đang lan truyền kia không?</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Dù sao, đó cũng là một kiệt tác do chính {Male=anh ấy;Female=cô ấy} chụp lại mà.</t>
+          <t>Dù sao, đó cũng là một kiệt tác do chính {Male=himself;Female=herself} chụp lại mà.</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Ta, Solvik, Muse và Flaer. Cả bốn đứa chúng ta.</t>
+          <t>Tao, Solvik, Muse và Flaer. Cả bốn đứa chúng tao.</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Ta à? Ta vẫn chưa quyết định được…</t>
+          <t>Tao à? Tao vẫn chưa quyết định được…</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Flaer, ta chỉ thấy toàn răng của ngươi thôi...</t>
+          <t>Flaer, tao chỉ thấy toàn răng của mày thôi...</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Musen, tóc ngươi che mất gần một phần năm mặt ta rồi đấy.</t>
+          <t>Musen, tóc mày che mất gần một phần năm mặt tao rồi đấy.</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Điểm đến tiếp theo… Ta nên kiểm tra mấy phòng học đã.</t>
+          <t>Điểm đến tiếp theo… Tao nên kiểm tra mấy phòng học đã.</t>
         </is>
       </c>
     </row>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Hello.</t>
+          <t>Xin chào.</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Dù sao giờ ta cũng không còn là lính mới nữa.</t>
+          <t>Dù sao giờ tao cũng không còn là lính mới nữa.</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Nếu cái lon đó là lựu đạn, cậu đã tự thổi bay nửa người mình rồi!</t>
+          <t>Nếu cái lon đó là lựu đạn, mày đã tự thổi bay nửa người mình rồi!</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Bên đó có vẻ náo nhiệt đấy. Ta nên qua xem thử.</t>
+          <t>Bên đó có vẻ náo nhiệt đấy. Tao nên qua xem thử.</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Được! Làm sao ta bỏ lỡ thứ thú vị thế này được? Nhưng mà...</t>
+          <t>Được! Làm sao tao bỏ lỡ thứ thú vị thế này được? Nhưng mà...</t>
         </is>
       </c>
     </row>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Haha! Nếu ngươi ngừng cười toe toét, có khi người ta tưởng tụi mình đứng đây chịu phạt đấy.</t>
+          <t>Haha! Nếu mày ngừng cười toe toét, có khi người ta tưởng tụi mình đứng đây chịu phạt đấy.</t>
         </is>
       </c>
     </row>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Chắc chắn rồi.</t>
+          <t>Được thôi.</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Tất nhiên rồi.</t>
+          <t>Đương nhiên.</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Ta nghe ngươi nhắc đến cái tên đó lúc nãy. Bạn của ngươi à?</t>
+          <t>Tao nghe mày nhắc đến cái tên đó lúc nãy. Bạn của mày à?</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Mỗi khi gặp rắc rối, cô ấy đều giúp ta thoát hiểm. Rồi đến đêm, chúng ta lại cùng ngắm sao.</t>
+          <t>Mỗi khi gặp rắc rối, cô ấy đều giúp tao thoát hiểm. Rồi đến đêm, chúng tao lại cùng ngắm sao.</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Ta nghe ngươi nhắc đến cái tên đó lúc nãy. Bạn của ngươi à?</t>
+          <t>Tao nghe mày nhắc đến cái tên đó lúc nãy. Bạn của mày à?</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Mỗi khi gặp rắc rối, cô ấy đều giúp ta thoát hiểm. Rồi đến đêm, chúng ta lại cùng ngắm sao.</t>
+          <t>Mỗi khi gặp rắc rối, cô ấy đều giúp tao thoát hiểm. Rồi đến đêm, chúng tao lại cùng ngắm sao.</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Có chuyện gì vậy?</t>
+          <t>Sao thế?</t>
         </is>
       </c>
     </row>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Ha. Ta là Jasper. Harriet có thể đã nhắc đến ta rồi.</t>
+          <t>Ha. Tao là Jasper. Harriet có thể đã nhắc đến tao rồi.</t>
         </is>
       </c>
     </row>
@@ -21049,7 +21049,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Gần đây, hầu hết các Mục Đồng ở Rừng Bjartr đều bận rộn với công việc, mỗi người phải chăm sóc hơn hai mươi Soliskin.</t>
+          <t>Gần đây, hầu hết các Mục Đồng ở Bjartr Woods đều bận rộn với công việc, mỗi người phải chăm sóc hơn hai mươi Soliskin.</t>
         </is>
       </c>
     </row>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Tất nhiên rồi.</t>
+          <t>Đương nhiên.</t>
         </is>
       </c>
     </row>
@@ -22739,7 +22739,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Hạt Soliseed của Essehalo là hạt giống của một Soliskin mới sinh, có thể coi như anh là {Male=bố;Female=mẹ} của chúng vậy.</t>
+          <t>Hạt Soliseed của Essehalo là hạt giống của một Soliskin mới sinh, có thể coi như anh là {Male=father;Female=mother} của chúng vậy.</t>
         </is>
       </c>
     </row>
